--- a/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.WS.RPR.04.04. Yıkama Bölümü Genel Günlük Üretim Raporu.xlsx
+++ b/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.WS.RPR.04.04. Yıkama Bölümü Genel Günlük Üretim Raporu.xlsx
@@ -207,7 +207,7 @@
     </r>
   </si>
   <si>
-    <t>EG.WS.RPR.04.04</t>
+    <t>EMS.WS.RPR.04.04</t>
   </si>
 </sst>
 </file>
